--- a/outputs/case10_witan.xlsx
+++ b/outputs/case10_witan.xlsx
@@ -821,9 +821,9 @@
       <x:c r="B11" s="0">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="e" cm="1">
-        <x:f t="array" ref="C11:C11">INDEX(Data!C2:C5,XMATCH("D",Data!A2:A5))</x:f>
-        <x:v>#VALUE!</x:v>
+      <x:c r="C11" s="0" cm="1">
+        <x:f t="array" ref="C11:C11">INDEX(Data!C2:C5,_xlfn.XMATCH("D",Data!A2:A5))</x:f>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
